--- a/AtchisonRegime/Outputs/USA/USA500_Financials/df_regSummary_USA500_Financials.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Financials/df_regSummary_USA500_Financials.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>2.29098455622489</v>
+        <v>2.281315888815698</v>
       </c>
       <c r="H2" t="n">
-        <v>4.517860264604721</v>
+        <v>4.481934865700838</v>
       </c>
       <c r="I2" t="n">
         <v>-7.834552959385981</v>
@@ -545,16 +545,16 @@
         <v>14.7955721617363</v>
       </c>
       <c r="K2" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3497317708204247</v>
+        <v>0.3551572469557611</v>
       </c>
       <c r="O2" t="n">
         <v>-0.04384403286972716</v>
@@ -603,7 +603,7 @@
         <v>17.2630481734445</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L3" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>9.959724493416481</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
@@ -719,7 +719,7 @@
         <v>12.5443599847335</v>
       </c>
       <c r="K5" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
